--- a/雅各組出席表.xlsx
+++ b/雅各組出席表.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
   <si>
     <t>序號</t>
   </si>
@@ -583,7 +583,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:5" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,10 +684,14 @@
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -802,7 +806,9 @@
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
         <v>23</v>
@@ -815,7 +821,9 @@
       <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
         <v>23</v>
@@ -832,5 +840,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/雅各組出席表.xlsx
+++ b/雅各組出席表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fung\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fung\jacob-attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>序號</t>
   </si>
@@ -608,9 +608,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
@@ -625,9 +623,7 @@
       <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
         <v>23</v>
       </c>
@@ -655,9 +651,7 @@
       <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -670,9 +664,7 @@
       <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
@@ -687,9 +679,7 @@
       <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
         <v>22</v>
       </c>
@@ -704,9 +694,7 @@
       <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -719,9 +707,7 @@
       <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
         <v>22</v>
       </c>
@@ -734,9 +720,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
         <v>23</v>
       </c>
@@ -749,9 +733,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
         <v>23</v>
       </c>
@@ -764,9 +746,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -779,9 +759,7 @@
       <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">

--- a/雅各組出席表.xlsx
+++ b/雅各組出席表.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t>序號</t>
   </si>
@@ -707,7 +707,9 @@
       <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>22</v>
       </c>
@@ -720,7 +722,9 @@
         <v>5</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>23</v>
       </c>
@@ -733,7 +737,9 @@
         <v>16</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>23</v>
       </c>
@@ -746,7 +752,9 @@
         <v>17</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">

--- a/雅各組出席表.xlsx
+++ b/雅各組出席表.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>序號</t>
   </si>
@@ -608,7 +608,9 @@
         <v>13</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
@@ -623,7 +625,9 @@
       <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>23</v>
       </c>
@@ -638,7 +642,9 @@
       <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -651,7 +657,9 @@
       <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">

--- a/雅各組出席表.xlsx
+++ b/雅各組出席表.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>序號</t>
   </si>
@@ -611,9 +611,7 @@
       <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
@@ -628,9 +626,7 @@
       <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
@@ -673,9 +669,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
@@ -688,9 +682,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
@@ -718,9 +710,7 @@
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
@@ -733,9 +723,7 @@
       <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
@@ -748,9 +736,7 @@
       <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
@@ -789,9 +775,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
@@ -804,9 +788,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
@@ -819,9 +801,7 @@
         <v>22</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
